--- a/downloads/gate-routing-map.xlsx
+++ b/downloads/gate-routing-map.xlsx
@@ -2316,7 +2316,7 @@
         <v/>
       </c>
       <c r="R9" s="8">
-        <f>IF(C9="","",IF(C9="Block",IF(OR(E9="",E9&lt;1),"No trials set",IF(F9="","Trials that must pass not set",IF(F9&lt;E9,"Trials that must pass is lower than trials",IF(F9&gt;E9,"Trials that must pass is more than trials",IF(AND(D9&lt;&gt;"Yes",E9&lt;$C$5),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C9="Human decides",IF(G9="","No owner",IF(I9&lt;&gt;"Yes","No halt criteria","")),IF(C9="Check downstream",IF(J9="","No downstream system named",IF(K9="","No team named for its pipeline",IF(L9="Partial","Output contract only partial",IF(L9&lt;&gt;"Yes","No output contract",IF(M9&lt;&gt;"Yes","Contract not verified before deploy",IF(N9&lt;&gt;"Yes","Cannot switch on together",IF(O9="","Nobody named who can halt",""))))))),IF(C9="Track",IF(P9="","No owner",""),"")))))</f>
+        <f>IF(C9="","",IF(C9="Block",IF(OR(E9="",E9&lt;1),"No trials set",IF(F9="","Trials that must pass not set",IF(F9&lt;E9,"Trials that must pass is lower than trials",IF(F9&gt;E9,"Trials that must pass is more than trials",IF(AND(D9&lt;&gt;"Yes",E9&lt;IF($C$5="",3,$C$5)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C9="Human decides",IF(G9="","No owner",IF(I9&lt;&gt;"Yes","No halt criteria","")),IF(C9="Check downstream",IF(J9="","No downstream system named",IF(K9="","No team named for its pipeline",IF(L9="Partial","Output contract only partial",IF(L9&lt;&gt;"Yes","No output contract",IF(M9&lt;&gt;"Yes","Contract not verified before deploy",IF(N9&lt;&gt;"Yes","Cannot switch on together",IF(O9="","Nobody named who can halt",""))))))),IF(C9="Track",IF(P9="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -2353,7 +2353,7 @@
         <v/>
       </c>
       <c r="R10" s="8">
-        <f>IF(C10="","",IF(C10="Block",IF(OR(E10="",E10&lt;1),"No trials set",IF(F10="","Trials that must pass not set",IF(F10&lt;E10,"Trials that must pass is lower than trials",IF(F10&gt;E10,"Trials that must pass is more than trials",IF(AND(D10&lt;&gt;"Yes",E10&lt;$C$5),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C10="Human decides",IF(G10="","No owner",IF(I10&lt;&gt;"Yes","No halt criteria","")),IF(C10="Check downstream",IF(J10="","No downstream system named",IF(K10="","No team named for its pipeline",IF(L10="Partial","Output contract only partial",IF(L10&lt;&gt;"Yes","No output contract",IF(M10&lt;&gt;"Yes","Contract not verified before deploy",IF(N10&lt;&gt;"Yes","Cannot switch on together",IF(O10="","Nobody named who can halt",""))))))),IF(C10="Track",IF(P10="","No owner",""),"")))))</f>
+        <f>IF(C10="","",IF(C10="Block",IF(OR(E10="",E10&lt;1),"No trials set",IF(F10="","Trials that must pass not set",IF(F10&lt;E10,"Trials that must pass is lower than trials",IF(F10&gt;E10,"Trials that must pass is more than trials",IF(AND(D10&lt;&gt;"Yes",E10&lt;IF($C$5="",3,$C$5)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C10="Human decides",IF(G10="","No owner",IF(I10&lt;&gt;"Yes","No halt criteria","")),IF(C10="Check downstream",IF(J10="","No downstream system named",IF(K10="","No team named for its pipeline",IF(L10="Partial","Output contract only partial",IF(L10&lt;&gt;"Yes","No output contract",IF(M10&lt;&gt;"Yes","Contract not verified before deploy",IF(N10&lt;&gt;"Yes","Cannot switch on together",IF(O10="","Nobody named who can halt",""))))))),IF(C10="Track",IF(P10="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
         <v/>
       </c>
       <c r="R11" s="8">
-        <f>IF(C11="","",IF(C11="Block",IF(OR(E11="",E11&lt;1),"No trials set",IF(F11="","Trials that must pass not set",IF(F11&lt;E11,"Trials that must pass is lower than trials",IF(F11&gt;E11,"Trials that must pass is more than trials",IF(AND(D11&lt;&gt;"Yes",E11&lt;$C$5),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C11="Human decides",IF(G11="","No owner",IF(I11&lt;&gt;"Yes","No halt criteria","")),IF(C11="Check downstream",IF(J11="","No downstream system named",IF(K11="","No team named for its pipeline",IF(L11="Partial","Output contract only partial",IF(L11&lt;&gt;"Yes","No output contract",IF(M11&lt;&gt;"Yes","Contract not verified before deploy",IF(N11&lt;&gt;"Yes","Cannot switch on together",IF(O11="","Nobody named who can halt",""))))))),IF(C11="Track",IF(P11="","No owner",""),"")))))</f>
+        <f>IF(C11="","",IF(C11="Block",IF(OR(E11="",E11&lt;1),"No trials set",IF(F11="","Trials that must pass not set",IF(F11&lt;E11,"Trials that must pass is lower than trials",IF(F11&gt;E11,"Trials that must pass is more than trials",IF(AND(D11&lt;&gt;"Yes",E11&lt;IF($C$5="",3,$C$5)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C11="Human decides",IF(G11="","No owner",IF(I11&lt;&gt;"Yes","No halt criteria","")),IF(C11="Check downstream",IF(J11="","No downstream system named",IF(K11="","No team named for its pipeline",IF(L11="Partial","Output contract only partial",IF(L11&lt;&gt;"Yes","No output contract",IF(M11&lt;&gt;"Yes","Contract not verified before deploy",IF(N11&lt;&gt;"Yes","Cannot switch on together",IF(O11="","Nobody named who can halt",""))))))),IF(C11="Track",IF(P11="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="R12" s="8">
-        <f>IF(C12="","",IF(C12="Block",IF(OR(E12="",E12&lt;1),"No trials set",IF(F12="","Trials that must pass not set",IF(F12&lt;E12,"Trials that must pass is lower than trials",IF(F12&gt;E12,"Trials that must pass is more than trials",IF(AND(D12&lt;&gt;"Yes",E12&lt;$C$5),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C12="Human decides",IF(G12="","No owner",IF(I12&lt;&gt;"Yes","No halt criteria","")),IF(C12="Check downstream",IF(J12="","No downstream system named",IF(K12="","No team named for its pipeline",IF(L12="Partial","Output contract only partial",IF(L12&lt;&gt;"Yes","No output contract",IF(M12&lt;&gt;"Yes","Contract not verified before deploy",IF(N12&lt;&gt;"Yes","Cannot switch on together",IF(O12="","Nobody named who can halt",""))))))),IF(C12="Track",IF(P12="","No owner",""),"")))))</f>
+        <f>IF(C12="","",IF(C12="Block",IF(OR(E12="",E12&lt;1),"No trials set",IF(F12="","Trials that must pass not set",IF(F12&lt;E12,"Trials that must pass is lower than trials",IF(F12&gt;E12,"Trials that must pass is more than trials",IF(AND(D12&lt;&gt;"Yes",E12&lt;IF($C$5="",3,$C$5)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C12="Human decides",IF(G12="","No owner",IF(I12&lt;&gt;"Yes","No halt criteria","")),IF(C12="Check downstream",IF(J12="","No downstream system named",IF(K12="","No team named for its pipeline",IF(L12="Partial","Output contract only partial",IF(L12&lt;&gt;"Yes","No output contract",IF(M12&lt;&gt;"Yes","Contract not verified before deploy",IF(N12&lt;&gt;"Yes","Cannot switch on together",IF(O12="","Nobody named who can halt",""))))))),IF(C12="Track",IF(P12="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -2464,7 +2464,7 @@
         <v/>
       </c>
       <c r="R13" s="8">
-        <f>IF(C13="","",IF(C13="Block",IF(OR(E13="",E13&lt;1),"No trials set",IF(F13="","Trials that must pass not set",IF(F13&lt;E13,"Trials that must pass is lower than trials",IF(F13&gt;E13,"Trials that must pass is more than trials",IF(AND(D13&lt;&gt;"Yes",E13&lt;$C$5),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C13="Human decides",IF(G13="","No owner",IF(I13&lt;&gt;"Yes","No halt criteria","")),IF(C13="Check downstream",IF(J13="","No downstream system named",IF(K13="","No team named for its pipeline",IF(L13="Partial","Output contract only partial",IF(L13&lt;&gt;"Yes","No output contract",IF(M13&lt;&gt;"Yes","Contract not verified before deploy",IF(N13&lt;&gt;"Yes","Cannot switch on together",IF(O13="","Nobody named who can halt",""))))))),IF(C13="Track",IF(P13="","No owner",""),"")))))</f>
+        <f>IF(C13="","",IF(C13="Block",IF(OR(E13="",E13&lt;1),"No trials set",IF(F13="","Trials that must pass not set",IF(F13&lt;E13,"Trials that must pass is lower than trials",IF(F13&gt;E13,"Trials that must pass is more than trials",IF(AND(D13&lt;&gt;"Yes",E13&lt;IF($C$5="",3,$C$5)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C13="Human decides",IF(G13="","No owner",IF(I13&lt;&gt;"Yes","No halt criteria","")),IF(C13="Check downstream",IF(J13="","No downstream system named",IF(K13="","No team named for its pipeline",IF(L13="Partial","Output contract only partial",IF(L13&lt;&gt;"Yes","No output contract",IF(M13&lt;&gt;"Yes","Contract not verified before deploy",IF(N13&lt;&gt;"Yes","Cannot switch on together",IF(O13="","Nobody named who can halt",""))))))),IF(C13="Track",IF(P13="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
         <v/>
       </c>
       <c r="R14" s="8">
-        <f>IF(C14="","",IF(C14="Block",IF(OR(E14="",E14&lt;1),"No trials set",IF(F14="","Trials that must pass not set",IF(F14&lt;E14,"Trials that must pass is lower than trials",IF(F14&gt;E14,"Trials that must pass is more than trials",IF(AND(D14&lt;&gt;"Yes",E14&lt;$C$5),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C14="Human decides",IF(G14="","No owner",IF(I14&lt;&gt;"Yes","No halt criteria","")),IF(C14="Check downstream",IF(J14="","No downstream system named",IF(K14="","No team named for its pipeline",IF(L14="Partial","Output contract only partial",IF(L14&lt;&gt;"Yes","No output contract",IF(M14&lt;&gt;"Yes","Contract not verified before deploy",IF(N14&lt;&gt;"Yes","Cannot switch on together",IF(O14="","Nobody named who can halt",""))))))),IF(C14="Track",IF(P14="","No owner",""),"")))))</f>
+        <f>IF(C14="","",IF(C14="Block",IF(OR(E14="",E14&lt;1),"No trials set",IF(F14="","Trials that must pass not set",IF(F14&lt;E14,"Trials that must pass is lower than trials",IF(F14&gt;E14,"Trials that must pass is more than trials",IF(AND(D14&lt;&gt;"Yes",E14&lt;IF($C$5="",3,$C$5)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C14="Human decides",IF(G14="","No owner",IF(I14&lt;&gt;"Yes","No halt criteria","")),IF(C14="Check downstream",IF(J14="","No downstream system named",IF(K14="","No team named for its pipeline",IF(L14="Partial","Output contract only partial",IF(L14&lt;&gt;"Yes","No output contract",IF(M14&lt;&gt;"Yes","Contract not verified before deploy",IF(N14&lt;&gt;"Yes","Cannot switch on together",IF(O14="","Nobody named who can halt",""))))))),IF(C14="Track",IF(P14="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -2538,7 +2538,7 @@
         <v/>
       </c>
       <c r="R15" s="8">
-        <f>IF(C15="","",IF(C15="Block",IF(OR(E15="",E15&lt;1),"No trials set",IF(F15="","Trials that must pass not set",IF(F15&lt;E15,"Trials that must pass is lower than trials",IF(F15&gt;E15,"Trials that must pass is more than trials",IF(AND(D15&lt;&gt;"Yes",E15&lt;$C$5),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C15="Human decides",IF(G15="","No owner",IF(I15&lt;&gt;"Yes","No halt criteria","")),IF(C15="Check downstream",IF(J15="","No downstream system named",IF(K15="","No team named for its pipeline",IF(L15="Partial","Output contract only partial",IF(L15&lt;&gt;"Yes","No output contract",IF(M15&lt;&gt;"Yes","Contract not verified before deploy",IF(N15&lt;&gt;"Yes","Cannot switch on together",IF(O15="","Nobody named who can halt",""))))))),IF(C15="Track",IF(P15="","No owner",""),"")))))</f>
+        <f>IF(C15="","",IF(C15="Block",IF(OR(E15="",E15&lt;1),"No trials set",IF(F15="","Trials that must pass not set",IF(F15&lt;E15,"Trials that must pass is lower than trials",IF(F15&gt;E15,"Trials that must pass is more than trials",IF(AND(D15&lt;&gt;"Yes",E15&lt;IF($C$5="",3,$C$5)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C15="Human decides",IF(G15="","No owner",IF(I15&lt;&gt;"Yes","No halt criteria","")),IF(C15="Check downstream",IF(J15="","No downstream system named",IF(K15="","No team named for its pipeline",IF(L15="Partial","Output contract only partial",IF(L15&lt;&gt;"Yes","No output contract",IF(M15&lt;&gt;"Yes","Contract not verified before deploy",IF(N15&lt;&gt;"Yes","Cannot switch on together",IF(O15="","Nobody named who can halt",""))))))),IF(C15="Track",IF(P15="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -2575,7 +2575,7 @@
         <v/>
       </c>
       <c r="R16" s="8">
-        <f>IF(C16="","",IF(C16="Block",IF(OR(E16="",E16&lt;1),"No trials set",IF(F16="","Trials that must pass not set",IF(F16&lt;E16,"Trials that must pass is lower than trials",IF(F16&gt;E16,"Trials that must pass is more than trials",IF(AND(D16&lt;&gt;"Yes",E16&lt;$C$5),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C16="Human decides",IF(G16="","No owner",IF(I16&lt;&gt;"Yes","No halt criteria","")),IF(C16="Check downstream",IF(J16="","No downstream system named",IF(K16="","No team named for its pipeline",IF(L16="Partial","Output contract only partial",IF(L16&lt;&gt;"Yes","No output contract",IF(M16&lt;&gt;"Yes","Contract not verified before deploy",IF(N16&lt;&gt;"Yes","Cannot switch on together",IF(O16="","Nobody named who can halt",""))))))),IF(C16="Track",IF(P16="","No owner",""),"")))))</f>
+        <f>IF(C16="","",IF(C16="Block",IF(OR(E16="",E16&lt;1),"No trials set",IF(F16="","Trials that must pass not set",IF(F16&lt;E16,"Trials that must pass is lower than trials",IF(F16&gt;E16,"Trials that must pass is more than trials",IF(AND(D16&lt;&gt;"Yes",E16&lt;IF($C$5="",3,$C$5)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C16="Human decides",IF(G16="","No owner",IF(I16&lt;&gt;"Yes","No halt criteria","")),IF(C16="Check downstream",IF(J16="","No downstream system named",IF(K16="","No team named for its pipeline",IF(L16="Partial","Output contract only partial",IF(L16&lt;&gt;"Yes","No output contract",IF(M16&lt;&gt;"Yes","Contract not verified before deploy",IF(N16&lt;&gt;"Yes","Cannot switch on together",IF(O16="","Nobody named who can halt",""))))))),IF(C16="Track",IF(P16="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
         <v/>
       </c>
       <c r="R17" s="8">
-        <f>IF(C17="","",IF(C17="Block",IF(OR(E17="",E17&lt;1),"No trials set",IF(F17="","Trials that must pass not set",IF(F17&lt;E17,"Trials that must pass is lower than trials",IF(F17&gt;E17,"Trials that must pass is more than trials",IF(AND(D17&lt;&gt;"Yes",E17&lt;$C$5),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C17="Human decides",IF(G17="","No owner",IF(I17&lt;&gt;"Yes","No halt criteria","")),IF(C17="Check downstream",IF(J17="","No downstream system named",IF(K17="","No team named for its pipeline",IF(L17="Partial","Output contract only partial",IF(L17&lt;&gt;"Yes","No output contract",IF(M17&lt;&gt;"Yes","Contract not verified before deploy",IF(N17&lt;&gt;"Yes","Cannot switch on together",IF(O17="","Nobody named who can halt",""))))))),IF(C17="Track",IF(P17="","No owner",""),"")))))</f>
+        <f>IF(C17="","",IF(C17="Block",IF(OR(E17="",E17&lt;1),"No trials set",IF(F17="","Trials that must pass not set",IF(F17&lt;E17,"Trials that must pass is lower than trials",IF(F17&gt;E17,"Trials that must pass is more than trials",IF(AND(D17&lt;&gt;"Yes",E17&lt;IF($C$5="",3,$C$5)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C17="Human decides",IF(G17="","No owner",IF(I17&lt;&gt;"Yes","No halt criteria","")),IF(C17="Check downstream",IF(J17="","No downstream system named",IF(K17="","No team named for its pipeline",IF(L17="Partial","Output contract only partial",IF(L17&lt;&gt;"Yes","No output contract",IF(M17&lt;&gt;"Yes","Contract not verified before deploy",IF(N17&lt;&gt;"Yes","Cannot switch on together",IF(O17="","Nobody named who can halt",""))))))),IF(C17="Track",IF(P17="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
         <v/>
       </c>
       <c r="R18" s="8">
-        <f>IF(C18="","",IF(C18="Block",IF(OR(E18="",E18&lt;1),"No trials set",IF(F18="","Trials that must pass not set",IF(F18&lt;E18,"Trials that must pass is lower than trials",IF(F18&gt;E18,"Trials that must pass is more than trials",IF(AND(D18&lt;&gt;"Yes",E18&lt;$C$5),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C18="Human decides",IF(G18="","No owner",IF(I18&lt;&gt;"Yes","No halt criteria","")),IF(C18="Check downstream",IF(J18="","No downstream system named",IF(K18="","No team named for its pipeline",IF(L18="Partial","Output contract only partial",IF(L18&lt;&gt;"Yes","No output contract",IF(M18&lt;&gt;"Yes","Contract not verified before deploy",IF(N18&lt;&gt;"Yes","Cannot switch on together",IF(O18="","Nobody named who can halt",""))))))),IF(C18="Track",IF(P18="","No owner",""),"")))))</f>
+        <f>IF(C18="","",IF(C18="Block",IF(OR(E18="",E18&lt;1),"No trials set",IF(F18="","Trials that must pass not set",IF(F18&lt;E18,"Trials that must pass is lower than trials",IF(F18&gt;E18,"Trials that must pass is more than trials",IF(AND(D18&lt;&gt;"Yes",E18&lt;IF($C$5="",3,$C$5)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C18="Human decides",IF(G18="","No owner",IF(I18&lt;&gt;"Yes","No halt criteria","")),IF(C18="Check downstream",IF(J18="","No downstream system named",IF(K18="","No team named for its pipeline",IF(L18="Partial","Output contract only partial",IF(L18&lt;&gt;"Yes","No output contract",IF(M18&lt;&gt;"Yes","Contract not verified before deploy",IF(N18&lt;&gt;"Yes","Cannot switch on together",IF(O18="","Nobody named who can halt",""))))))),IF(C18="Track",IF(P18="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
         <v/>
       </c>
       <c r="R19" s="8">
-        <f>IF(C19="","",IF(C19="Block",IF(OR(E19="",E19&lt;1),"No trials set",IF(F19="","Trials that must pass not set",IF(F19&lt;E19,"Trials that must pass is lower than trials",IF(F19&gt;E19,"Trials that must pass is more than trials",IF(AND(D19&lt;&gt;"Yes",E19&lt;$C$5),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C19="Human decides",IF(G19="","No owner",IF(I19&lt;&gt;"Yes","No halt criteria","")),IF(C19="Check downstream",IF(J19="","No downstream system named",IF(K19="","No team named for its pipeline",IF(L19="Partial","Output contract only partial",IF(L19&lt;&gt;"Yes","No output contract",IF(M19&lt;&gt;"Yes","Contract not verified before deploy",IF(N19&lt;&gt;"Yes","Cannot switch on together",IF(O19="","Nobody named who can halt",""))))))),IF(C19="Track",IF(P19="","No owner",""),"")))))</f>
+        <f>IF(C19="","",IF(C19="Block",IF(OR(E19="",E19&lt;1),"No trials set",IF(F19="","Trials that must pass not set",IF(F19&lt;E19,"Trials that must pass is lower than trials",IF(F19&gt;E19,"Trials that must pass is more than trials",IF(AND(D19&lt;&gt;"Yes",E19&lt;IF($C$5="",3,$C$5)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C19="Human decides",IF(G19="","No owner",IF(I19&lt;&gt;"Yes","No halt criteria","")),IF(C19="Check downstream",IF(J19="","No downstream system named",IF(K19="","No team named for its pipeline",IF(L19="Partial","Output contract only partial",IF(L19&lt;&gt;"Yes","No output contract",IF(M19&lt;&gt;"Yes","Contract not verified before deploy",IF(N19&lt;&gt;"Yes","Cannot switch on together",IF(O19="","Nobody named who can halt",""))))))),IF(C19="Track",IF(P19="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -2723,7 +2723,7 @@
         <v/>
       </c>
       <c r="R20" s="8">
-        <f>IF(C20="","",IF(C20="Block",IF(OR(E20="",E20&lt;1),"No trials set",IF(F20="","Trials that must pass not set",IF(F20&lt;E20,"Trials that must pass is lower than trials",IF(F20&gt;E20,"Trials that must pass is more than trials",IF(AND(D20&lt;&gt;"Yes",E20&lt;$C$5),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C20="Human decides",IF(G20="","No owner",IF(I20&lt;&gt;"Yes","No halt criteria","")),IF(C20="Check downstream",IF(J20="","No downstream system named",IF(K20="","No team named for its pipeline",IF(L20="Partial","Output contract only partial",IF(L20&lt;&gt;"Yes","No output contract",IF(M20&lt;&gt;"Yes","Contract not verified before deploy",IF(N20&lt;&gt;"Yes","Cannot switch on together",IF(O20="","Nobody named who can halt",""))))))),IF(C20="Track",IF(P20="","No owner",""),"")))))</f>
+        <f>IF(C20="","",IF(C20="Block",IF(OR(E20="",E20&lt;1),"No trials set",IF(F20="","Trials that must pass not set",IF(F20&lt;E20,"Trials that must pass is lower than trials",IF(F20&gt;E20,"Trials that must pass is more than trials",IF(AND(D20&lt;&gt;"Yes",E20&lt;IF($C$5="",3,$C$5)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C20="Human decides",IF(G20="","No owner",IF(I20&lt;&gt;"Yes","No halt criteria","")),IF(C20="Check downstream",IF(J20="","No downstream system named",IF(K20="","No team named for its pipeline",IF(L20="Partial","Output contract only partial",IF(L20&lt;&gt;"Yes","No output contract",IF(M20&lt;&gt;"Yes","Contract not verified before deploy",IF(N20&lt;&gt;"Yes","Cannot switch on together",IF(O20="","Nobody named who can halt",""))))))),IF(C20="Track",IF(P20="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
         <v/>
       </c>
       <c r="R21" s="8">
-        <f>IF(C21="","",IF(C21="Block",IF(OR(E21="",E21&lt;1),"No trials set",IF(F21="","Trials that must pass not set",IF(F21&lt;E21,"Trials that must pass is lower than trials",IF(F21&gt;E21,"Trials that must pass is more than trials",IF(AND(D21&lt;&gt;"Yes",E21&lt;$C$5),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C21="Human decides",IF(G21="","No owner",IF(I21&lt;&gt;"Yes","No halt criteria","")),IF(C21="Check downstream",IF(J21="","No downstream system named",IF(K21="","No team named for its pipeline",IF(L21="Partial","Output contract only partial",IF(L21&lt;&gt;"Yes","No output contract",IF(M21&lt;&gt;"Yes","Contract not verified before deploy",IF(N21&lt;&gt;"Yes","Cannot switch on together",IF(O21="","Nobody named who can halt",""))))))),IF(C21="Track",IF(P21="","No owner",""),"")))))</f>
+        <f>IF(C21="","",IF(C21="Block",IF(OR(E21="",E21&lt;1),"No trials set",IF(F21="","Trials that must pass not set",IF(F21&lt;E21,"Trials that must pass is lower than trials",IF(F21&gt;E21,"Trials that must pass is more than trials",IF(AND(D21&lt;&gt;"Yes",E21&lt;IF($C$5="",3,$C$5)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C21="Human decides",IF(G21="","No owner",IF(I21&lt;&gt;"Yes","No halt criteria","")),IF(C21="Check downstream",IF(J21="","No downstream system named",IF(K21="","No team named for its pipeline",IF(L21="Partial","Output contract only partial",IF(L21&lt;&gt;"Yes","No output contract",IF(M21&lt;&gt;"Yes","Contract not verified before deploy",IF(N21&lt;&gt;"Yes","Cannot switch on together",IF(O21="","Nobody named who can halt",""))))))),IF(C21="Track",IF(P21="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
         <v/>
       </c>
       <c r="R22" s="8">
-        <f>IF(C22="","",IF(C22="Block",IF(OR(E22="",E22&lt;1),"No trials set",IF(F22="","Trials that must pass not set",IF(F22&lt;E22,"Trials that must pass is lower than trials",IF(F22&gt;E22,"Trials that must pass is more than trials",IF(AND(D22&lt;&gt;"Yes",E22&lt;$C$5),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C22="Human decides",IF(G22="","No owner",IF(I22&lt;&gt;"Yes","No halt criteria","")),IF(C22="Check downstream",IF(J22="","No downstream system named",IF(K22="","No team named for its pipeline",IF(L22="Partial","Output contract only partial",IF(L22&lt;&gt;"Yes","No output contract",IF(M22&lt;&gt;"Yes","Contract not verified before deploy",IF(N22&lt;&gt;"Yes","Cannot switch on together",IF(O22="","Nobody named who can halt",""))))))),IF(C22="Track",IF(P22="","No owner",""),"")))))</f>
+        <f>IF(C22="","",IF(C22="Block",IF(OR(E22="",E22&lt;1),"No trials set",IF(F22="","Trials that must pass not set",IF(F22&lt;E22,"Trials that must pass is lower than trials",IF(F22&gt;E22,"Trials that must pass is more than trials",IF(AND(D22&lt;&gt;"Yes",E22&lt;IF($C$5="",3,$C$5)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C22="Human decides",IF(G22="","No owner",IF(I22&lt;&gt;"Yes","No halt criteria","")),IF(C22="Check downstream",IF(J22="","No downstream system named",IF(K22="","No team named for its pipeline",IF(L22="Partial","Output contract only partial",IF(L22&lt;&gt;"Yes","No output contract",IF(M22&lt;&gt;"Yes","Contract not verified before deploy",IF(N22&lt;&gt;"Yes","Cannot switch on together",IF(O22="","Nobody named who can halt",""))))))),IF(C22="Track",IF(P22="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
         <v/>
       </c>
       <c r="R23" s="8">
-        <f>IF(C23="","",IF(C23="Block",IF(OR(E23="",E23&lt;1),"No trials set",IF(F23="","Trials that must pass not set",IF(F23&lt;E23,"Trials that must pass is lower than trials",IF(F23&gt;E23,"Trials that must pass is more than trials",IF(AND(D23&lt;&gt;"Yes",E23&lt;$C$5),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C23="Human decides",IF(G23="","No owner",IF(I23&lt;&gt;"Yes","No halt criteria","")),IF(C23="Check downstream",IF(J23="","No downstream system named",IF(K23="","No team named for its pipeline",IF(L23="Partial","Output contract only partial",IF(L23&lt;&gt;"Yes","No output contract",IF(M23&lt;&gt;"Yes","Contract not verified before deploy",IF(N23&lt;&gt;"Yes","Cannot switch on together",IF(O23="","Nobody named who can halt",""))))))),IF(C23="Track",IF(P23="","No owner",""),"")))))</f>
+        <f>IF(C23="","",IF(C23="Block",IF(OR(E23="",E23&lt;1),"No trials set",IF(F23="","Trials that must pass not set",IF(F23&lt;E23,"Trials that must pass is lower than trials",IF(F23&gt;E23,"Trials that must pass is more than trials",IF(AND(D23&lt;&gt;"Yes",E23&lt;IF($C$5="",3,$C$5)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C23="Human decides",IF(G23="","No owner",IF(I23&lt;&gt;"Yes","No halt criteria","")),IF(C23="Check downstream",IF(J23="","No downstream system named",IF(K23="","No team named for its pipeline",IF(L23="Partial","Output contract only partial",IF(L23&lt;&gt;"Yes","No output contract",IF(M23&lt;&gt;"Yes","Contract not verified before deploy",IF(N23&lt;&gt;"Yes","Cannot switch on together",IF(O23="","Nobody named who can halt",""))))))),IF(C23="Track",IF(P23="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -2871,7 +2871,7 @@
         <v/>
       </c>
       <c r="R24" s="8">
-        <f>IF(C24="","",IF(C24="Block",IF(OR(E24="",E24&lt;1),"No trials set",IF(F24="","Trials that must pass not set",IF(F24&lt;E24,"Trials that must pass is lower than trials",IF(F24&gt;E24,"Trials that must pass is more than trials",IF(AND(D24&lt;&gt;"Yes",E24&lt;$C$5),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C24="Human decides",IF(G24="","No owner",IF(I24&lt;&gt;"Yes","No halt criteria","")),IF(C24="Check downstream",IF(J24="","No downstream system named",IF(K24="","No team named for its pipeline",IF(L24="Partial","Output contract only partial",IF(L24&lt;&gt;"Yes","No output contract",IF(M24&lt;&gt;"Yes","Contract not verified before deploy",IF(N24&lt;&gt;"Yes","Cannot switch on together",IF(O24="","Nobody named who can halt",""))))))),IF(C24="Track",IF(P24="","No owner",""),"")))))</f>
+        <f>IF(C24="","",IF(C24="Block",IF(OR(E24="",E24&lt;1),"No trials set",IF(F24="","Trials that must pass not set",IF(F24&lt;E24,"Trials that must pass is lower than trials",IF(F24&gt;E24,"Trials that must pass is more than trials",IF(AND(D24&lt;&gt;"Yes",E24&lt;IF($C$5="",3,$C$5)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C24="Human decides",IF(G24="","No owner",IF(I24&lt;&gt;"Yes","No halt criteria","")),IF(C24="Check downstream",IF(J24="","No downstream system named",IF(K24="","No team named for its pipeline",IF(L24="Partial","Output contract only partial",IF(L24&lt;&gt;"Yes","No output contract",IF(M24&lt;&gt;"Yes","Contract not verified before deploy",IF(N24&lt;&gt;"Yes","Cannot switch on together",IF(O24="","Nobody named who can halt",""))))))),IF(C24="Track",IF(P24="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
         <v/>
       </c>
       <c r="R25" s="8">
-        <f>IF(C25="","",IF(C25="Block",IF(OR(E25="",E25&lt;1),"No trials set",IF(F25="","Trials that must pass not set",IF(F25&lt;E25,"Trials that must pass is lower than trials",IF(F25&gt;E25,"Trials that must pass is more than trials",IF(AND(D25&lt;&gt;"Yes",E25&lt;$C$5),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C25="Human decides",IF(G25="","No owner",IF(I25&lt;&gt;"Yes","No halt criteria","")),IF(C25="Check downstream",IF(J25="","No downstream system named",IF(K25="","No team named for its pipeline",IF(L25="Partial","Output contract only partial",IF(L25&lt;&gt;"Yes","No output contract",IF(M25&lt;&gt;"Yes","Contract not verified before deploy",IF(N25&lt;&gt;"Yes","Cannot switch on together",IF(O25="","Nobody named who can halt",""))))))),IF(C25="Track",IF(P25="","No owner",""),"")))))</f>
+        <f>IF(C25="","",IF(C25="Block",IF(OR(E25="",E25&lt;1),"No trials set",IF(F25="","Trials that must pass not set",IF(F25&lt;E25,"Trials that must pass is lower than trials",IF(F25&gt;E25,"Trials that must pass is more than trials",IF(AND(D25&lt;&gt;"Yes",E25&lt;IF($C$5="",3,$C$5)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C25="Human decides",IF(G25="","No owner",IF(I25&lt;&gt;"Yes","No halt criteria","")),IF(C25="Check downstream",IF(J25="","No downstream system named",IF(K25="","No team named for its pipeline",IF(L25="Partial","Output contract only partial",IF(L25&lt;&gt;"Yes","No output contract",IF(M25&lt;&gt;"Yes","Contract not verified before deploy",IF(N25&lt;&gt;"Yes","Cannot switch on together",IF(O25="","Nobody named who can halt",""))))))),IF(C25="Track",IF(P25="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
         <v/>
       </c>
       <c r="R26" s="8">
-        <f>IF(C26="","",IF(C26="Block",IF(OR(E26="",E26&lt;1),"No trials set",IF(F26="","Trials that must pass not set",IF(F26&lt;E26,"Trials that must pass is lower than trials",IF(F26&gt;E26,"Trials that must pass is more than trials",IF(AND(D26&lt;&gt;"Yes",E26&lt;$C$5),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C26="Human decides",IF(G26="","No owner",IF(I26&lt;&gt;"Yes","No halt criteria","")),IF(C26="Check downstream",IF(J26="","No downstream system named",IF(K26="","No team named for its pipeline",IF(L26="Partial","Output contract only partial",IF(L26&lt;&gt;"Yes","No output contract",IF(M26&lt;&gt;"Yes","Contract not verified before deploy",IF(N26&lt;&gt;"Yes","Cannot switch on together",IF(O26="","Nobody named who can halt",""))))))),IF(C26="Track",IF(P26="","No owner",""),"")))))</f>
+        <f>IF(C26="","",IF(C26="Block",IF(OR(E26="",E26&lt;1),"No trials set",IF(F26="","Trials that must pass not set",IF(F26&lt;E26,"Trials that must pass is lower than trials",IF(F26&gt;E26,"Trials that must pass is more than trials",IF(AND(D26&lt;&gt;"Yes",E26&lt;IF($C$5="",3,$C$5)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C26="Human decides",IF(G26="","No owner",IF(I26&lt;&gt;"Yes","No halt criteria","")),IF(C26="Check downstream",IF(J26="","No downstream system named",IF(K26="","No team named for its pipeline",IF(L26="Partial","Output contract only partial",IF(L26&lt;&gt;"Yes","No output contract",IF(M26&lt;&gt;"Yes","Contract not verified before deploy",IF(N26&lt;&gt;"Yes","Cannot switch on together",IF(O26="","Nobody named who can halt",""))))))),IF(C26="Track",IF(P26="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
         <v/>
       </c>
       <c r="R27" s="8">
-        <f>IF(C27="","",IF(C27="Block",IF(OR(E27="",E27&lt;1),"No trials set",IF(F27="","Trials that must pass not set",IF(F27&lt;E27,"Trials that must pass is lower than trials",IF(F27&gt;E27,"Trials that must pass is more than trials",IF(AND(D27&lt;&gt;"Yes",E27&lt;$C$5),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C27="Human decides",IF(G27="","No owner",IF(I27&lt;&gt;"Yes","No halt criteria","")),IF(C27="Check downstream",IF(J27="","No downstream system named",IF(K27="","No team named for its pipeline",IF(L27="Partial","Output contract only partial",IF(L27&lt;&gt;"Yes","No output contract",IF(M27&lt;&gt;"Yes","Contract not verified before deploy",IF(N27&lt;&gt;"Yes","Cannot switch on together",IF(O27="","Nobody named who can halt",""))))))),IF(C27="Track",IF(P27="","No owner",""),"")))))</f>
+        <f>IF(C27="","",IF(C27="Block",IF(OR(E27="",E27&lt;1),"No trials set",IF(F27="","Trials that must pass not set",IF(F27&lt;E27,"Trials that must pass is lower than trials",IF(F27&gt;E27,"Trials that must pass is more than trials",IF(AND(D27&lt;&gt;"Yes",E27&lt;IF($C$5="",3,$C$5)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C27="Human decides",IF(G27="","No owner",IF(I27&lt;&gt;"Yes","No halt criteria","")),IF(C27="Check downstream",IF(J27="","No downstream system named",IF(K27="","No team named for its pipeline",IF(L27="Partial","Output contract only partial",IF(L27&lt;&gt;"Yes","No output contract",IF(M27&lt;&gt;"Yes","Contract not verified before deploy",IF(N27&lt;&gt;"Yes","Cannot switch on together",IF(O27="","Nobody named who can halt",""))))))),IF(C27="Track",IF(P27="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -3019,7 +3019,7 @@
         <v/>
       </c>
       <c r="R28" s="8">
-        <f>IF(C28="","",IF(C28="Block",IF(OR(E28="",E28&lt;1),"No trials set",IF(F28="","Trials that must pass not set",IF(F28&lt;E28,"Trials that must pass is lower than trials",IF(F28&gt;E28,"Trials that must pass is more than trials",IF(AND(D28&lt;&gt;"Yes",E28&lt;$C$5),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C28="Human decides",IF(G28="","No owner",IF(I28&lt;&gt;"Yes","No halt criteria","")),IF(C28="Check downstream",IF(J28="","No downstream system named",IF(K28="","No team named for its pipeline",IF(L28="Partial","Output contract only partial",IF(L28&lt;&gt;"Yes","No output contract",IF(M28&lt;&gt;"Yes","Contract not verified before deploy",IF(N28&lt;&gt;"Yes","Cannot switch on together",IF(O28="","Nobody named who can halt",""))))))),IF(C28="Track",IF(P28="","No owner",""),"")))))</f>
+        <f>IF(C28="","",IF(C28="Block",IF(OR(E28="",E28&lt;1),"No trials set",IF(F28="","Trials that must pass not set",IF(F28&lt;E28,"Trials that must pass is lower than trials",IF(F28&gt;E28,"Trials that must pass is more than trials",IF(AND(D28&lt;&gt;"Yes",E28&lt;IF($C$5="",3,$C$5)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C28="Human decides",IF(G28="","No owner",IF(I28&lt;&gt;"Yes","No halt criteria","")),IF(C28="Check downstream",IF(J28="","No downstream system named",IF(K28="","No team named for its pipeline",IF(L28="Partial","Output contract only partial",IF(L28&lt;&gt;"Yes","No output contract",IF(M28&lt;&gt;"Yes","Contract not verified before deploy",IF(N28&lt;&gt;"Yes","Cannot switch on together",IF(O28="","Nobody named who can halt",""))))))),IF(C28="Track",IF(P28="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
         <v/>
       </c>
       <c r="R51" s="8">
-        <f>IF(C51="","",IF(C51="Block",IF(OR(E51="",E51&lt;1),"No trials set",IF(F51="","Trials that must pass not set",IF(F51&lt;E51,"Trials that must pass is lower than trials",IF(F51&gt;E51,"Trials that must pass is more than trials",IF(AND(D51&lt;&gt;"Yes",E51&lt;$C$47),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C51="Human decides",IF(G51="","No owner",IF(I51&lt;&gt;"Yes","No halt criteria","")),IF(C51="Check downstream",IF(J51="","No downstream system named",IF(K51="","No team named for its pipeline",IF(L51="Partial","Output contract only partial",IF(L51&lt;&gt;"Yes","No output contract",IF(M51&lt;&gt;"Yes","Contract not verified before deploy",IF(N51&lt;&gt;"Yes","Cannot switch on together",IF(O51="","Nobody named who can halt",""))))))),IF(C51="Track",IF(P51="","No owner",""),"")))))</f>
+        <f>IF(C51="","",IF(C51="Block",IF(OR(E51="",E51&lt;1),"No trials set",IF(F51="","Trials that must pass not set",IF(F51&lt;E51,"Trials that must pass is lower than trials",IF(F51&gt;E51,"Trials that must pass is more than trials",IF(AND(D51&lt;&gt;"Yes",E51&lt;IF($C$47="",3,$C$47)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C51="Human decides",IF(G51="","No owner",IF(I51&lt;&gt;"Yes","No halt criteria","")),IF(C51="Check downstream",IF(J51="","No downstream system named",IF(K51="","No team named for its pipeline",IF(L51="Partial","Output contract only partial",IF(L51&lt;&gt;"Yes","No output contract",IF(M51&lt;&gt;"Yes","Contract not verified before deploy",IF(N51&lt;&gt;"Yes","Cannot switch on together",IF(O51="","Nobody named who can halt",""))))))),IF(C51="Track",IF(P51="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -5162,7 +5162,7 @@
         <v/>
       </c>
       <c r="R52" s="8">
-        <f>IF(C52="","",IF(C52="Block",IF(OR(E52="",E52&lt;1),"No trials set",IF(F52="","Trials that must pass not set",IF(F52&lt;E52,"Trials that must pass is lower than trials",IF(F52&gt;E52,"Trials that must pass is more than trials",IF(AND(D52&lt;&gt;"Yes",E52&lt;$C$47),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C52="Human decides",IF(G52="","No owner",IF(I52&lt;&gt;"Yes","No halt criteria","")),IF(C52="Check downstream",IF(J52="","No downstream system named",IF(K52="","No team named for its pipeline",IF(L52="Partial","Output contract only partial",IF(L52&lt;&gt;"Yes","No output contract",IF(M52&lt;&gt;"Yes","Contract not verified before deploy",IF(N52&lt;&gt;"Yes","Cannot switch on together",IF(O52="","Nobody named who can halt",""))))))),IF(C52="Track",IF(P52="","No owner",""),"")))))</f>
+        <f>IF(C52="","",IF(C52="Block",IF(OR(E52="",E52&lt;1),"No trials set",IF(F52="","Trials that must pass not set",IF(F52&lt;E52,"Trials that must pass is lower than trials",IF(F52&gt;E52,"Trials that must pass is more than trials",IF(AND(D52&lt;&gt;"Yes",E52&lt;IF($C$47="",3,$C$47)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C52="Human decides",IF(G52="","No owner",IF(I52&lt;&gt;"Yes","No halt criteria","")),IF(C52="Check downstream",IF(J52="","No downstream system named",IF(K52="","No team named for its pipeline",IF(L52="Partial","Output contract only partial",IF(L52&lt;&gt;"Yes","No output contract",IF(M52&lt;&gt;"Yes","Contract not verified before deploy",IF(N52&lt;&gt;"Yes","Cannot switch on together",IF(O52="","Nobody named who can halt",""))))))),IF(C52="Track",IF(P52="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
         <v/>
       </c>
       <c r="R53" s="8">
-        <f>IF(C53="","",IF(C53="Block",IF(OR(E53="",E53&lt;1),"No trials set",IF(F53="","Trials that must pass not set",IF(F53&lt;E53,"Trials that must pass is lower than trials",IF(F53&gt;E53,"Trials that must pass is more than trials",IF(AND(D53&lt;&gt;"Yes",E53&lt;$C$47),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C53="Human decides",IF(G53="","No owner",IF(I53&lt;&gt;"Yes","No halt criteria","")),IF(C53="Check downstream",IF(J53="","No downstream system named",IF(K53="","No team named for its pipeline",IF(L53="Partial","Output contract only partial",IF(L53&lt;&gt;"Yes","No output contract",IF(M53&lt;&gt;"Yes","Contract not verified before deploy",IF(N53&lt;&gt;"Yes","Cannot switch on together",IF(O53="","Nobody named who can halt",""))))))),IF(C53="Track",IF(P53="","No owner",""),"")))))</f>
+        <f>IF(C53="","",IF(C53="Block",IF(OR(E53="",E53&lt;1),"No trials set",IF(F53="","Trials that must pass not set",IF(F53&lt;E53,"Trials that must pass is lower than trials",IF(F53&gt;E53,"Trials that must pass is more than trials",IF(AND(D53&lt;&gt;"Yes",E53&lt;IF($C$47="",3,$C$47)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C53="Human decides",IF(G53="","No owner",IF(I53&lt;&gt;"Yes","No halt criteria","")),IF(C53="Check downstream",IF(J53="","No downstream system named",IF(K53="","No team named for its pipeline",IF(L53="Partial","Output contract only partial",IF(L53&lt;&gt;"Yes","No output contract",IF(M53&lt;&gt;"Yes","Contract not verified before deploy",IF(N53&lt;&gt;"Yes","Cannot switch on together",IF(O53="","Nobody named who can halt",""))))))),IF(C53="Track",IF(P53="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
         <v/>
       </c>
       <c r="R54" s="8">
-        <f>IF(C54="","",IF(C54="Block",IF(OR(E54="",E54&lt;1),"No trials set",IF(F54="","Trials that must pass not set",IF(F54&lt;E54,"Trials that must pass is lower than trials",IF(F54&gt;E54,"Trials that must pass is more than trials",IF(AND(D54&lt;&gt;"Yes",E54&lt;$C$47),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C54="Human decides",IF(G54="","No owner",IF(I54&lt;&gt;"Yes","No halt criteria","")),IF(C54="Check downstream",IF(J54="","No downstream system named",IF(K54="","No team named for its pipeline",IF(L54="Partial","Output contract only partial",IF(L54&lt;&gt;"Yes","No output contract",IF(M54&lt;&gt;"Yes","Contract not verified before deploy",IF(N54&lt;&gt;"Yes","Cannot switch on together",IF(O54="","Nobody named who can halt",""))))))),IF(C54="Track",IF(P54="","No owner",""),"")))))</f>
+        <f>IF(C54="","",IF(C54="Block",IF(OR(E54="",E54&lt;1),"No trials set",IF(F54="","Trials that must pass not set",IF(F54&lt;E54,"Trials that must pass is lower than trials",IF(F54&gt;E54,"Trials that must pass is more than trials",IF(AND(D54&lt;&gt;"Yes",E54&lt;IF($C$47="",3,$C$47)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C54="Human decides",IF(G54="","No owner",IF(I54&lt;&gt;"Yes","No halt criteria","")),IF(C54="Check downstream",IF(J54="","No downstream system named",IF(K54="","No team named for its pipeline",IF(L54="Partial","Output contract only partial",IF(L54&lt;&gt;"Yes","No output contract",IF(M54&lt;&gt;"Yes","Contract not verified before deploy",IF(N54&lt;&gt;"Yes","Cannot switch on together",IF(O54="","Nobody named who can halt",""))))))),IF(C54="Track",IF(P54="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -5289,7 +5289,7 @@
         <v/>
       </c>
       <c r="R55" s="8">
-        <f>IF(C55="","",IF(C55="Block",IF(OR(E55="",E55&lt;1),"No trials set",IF(F55="","Trials that must pass not set",IF(F55&lt;E55,"Trials that must pass is lower than trials",IF(F55&gt;E55,"Trials that must pass is more than trials",IF(AND(D55&lt;&gt;"Yes",E55&lt;$C$47),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C55="Human decides",IF(G55="","No owner",IF(I55&lt;&gt;"Yes","No halt criteria","")),IF(C55="Check downstream",IF(J55="","No downstream system named",IF(K55="","No team named for its pipeline",IF(L55="Partial","Output contract only partial",IF(L55&lt;&gt;"Yes","No output contract",IF(M55&lt;&gt;"Yes","Contract not verified before deploy",IF(N55&lt;&gt;"Yes","Cannot switch on together",IF(O55="","Nobody named who can halt",""))))))),IF(C55="Track",IF(P55="","No owner",""),"")))))</f>
+        <f>IF(C55="","",IF(C55="Block",IF(OR(E55="",E55&lt;1),"No trials set",IF(F55="","Trials that must pass not set",IF(F55&lt;E55,"Trials that must pass is lower than trials",IF(F55&gt;E55,"Trials that must pass is more than trials",IF(AND(D55&lt;&gt;"Yes",E55&lt;IF($C$47="",3,$C$47)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C55="Human decides",IF(G55="","No owner",IF(I55&lt;&gt;"Yes","No halt criteria","")),IF(C55="Check downstream",IF(J55="","No downstream system named",IF(K55="","No team named for its pipeline",IF(L55="Partial","Output contract only partial",IF(L55&lt;&gt;"Yes","No output contract",IF(M55&lt;&gt;"Yes","Contract not verified before deploy",IF(N55&lt;&gt;"Yes","Cannot switch on together",IF(O55="","Nobody named who can halt",""))))))),IF(C55="Track",IF(P55="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
         <v/>
       </c>
       <c r="R56" s="8">
-        <f>IF(C56="","",IF(C56="Block",IF(OR(E56="",E56&lt;1),"No trials set",IF(F56="","Trials that must pass not set",IF(F56&lt;E56,"Trials that must pass is lower than trials",IF(F56&gt;E56,"Trials that must pass is more than trials",IF(AND(D56&lt;&gt;"Yes",E56&lt;$C$47),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C56="Human decides",IF(G56="","No owner",IF(I56&lt;&gt;"Yes","No halt criteria","")),IF(C56="Check downstream",IF(J56="","No downstream system named",IF(K56="","No team named for its pipeline",IF(L56="Partial","Output contract only partial",IF(L56&lt;&gt;"Yes","No output contract",IF(M56&lt;&gt;"Yes","Contract not verified before deploy",IF(N56&lt;&gt;"Yes","Cannot switch on together",IF(O56="","Nobody named who can halt",""))))))),IF(C56="Track",IF(P56="","No owner",""),"")))))</f>
+        <f>IF(C56="","",IF(C56="Block",IF(OR(E56="",E56&lt;1),"No trials set",IF(F56="","Trials that must pass not set",IF(F56&lt;E56,"Trials that must pass is lower than trials",IF(F56&gt;E56,"Trials that must pass is more than trials",IF(AND(D56&lt;&gt;"Yes",E56&lt;IF($C$47="",3,$C$47)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C56="Human decides",IF(G56="","No owner",IF(I56&lt;&gt;"Yes","No halt criteria","")),IF(C56="Check downstream",IF(J56="","No downstream system named",IF(K56="","No team named for its pipeline",IF(L56="Partial","Output contract only partial",IF(L56&lt;&gt;"Yes","No output contract",IF(M56&lt;&gt;"Yes","Contract not verified before deploy",IF(N56&lt;&gt;"Yes","Cannot switch on together",IF(O56="","Nobody named who can halt",""))))))),IF(C56="Track",IF(P56="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -5367,7 +5367,7 @@
         <v/>
       </c>
       <c r="R57" s="8">
-        <f>IF(C57="","",IF(C57="Block",IF(OR(E57="",E57&lt;1),"No trials set",IF(F57="","Trials that must pass not set",IF(F57&lt;E57,"Trials that must pass is lower than trials",IF(F57&gt;E57,"Trials that must pass is more than trials",IF(AND(D57&lt;&gt;"Yes",E57&lt;$C$47),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C57="Human decides",IF(G57="","No owner",IF(I57&lt;&gt;"Yes","No halt criteria","")),IF(C57="Check downstream",IF(J57="","No downstream system named",IF(K57="","No team named for its pipeline",IF(L57="Partial","Output contract only partial",IF(L57&lt;&gt;"Yes","No output contract",IF(M57&lt;&gt;"Yes","Contract not verified before deploy",IF(N57&lt;&gt;"Yes","Cannot switch on together",IF(O57="","Nobody named who can halt",""))))))),IF(C57="Track",IF(P57="","No owner",""),"")))))</f>
+        <f>IF(C57="","",IF(C57="Block",IF(OR(E57="",E57&lt;1),"No trials set",IF(F57="","Trials that must pass not set",IF(F57&lt;E57,"Trials that must pass is lower than trials",IF(F57&gt;E57,"Trials that must pass is more than trials",IF(AND(D57&lt;&gt;"Yes",E57&lt;IF($C$47="",3,$C$47)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C57="Human decides",IF(G57="","No owner",IF(I57&lt;&gt;"Yes","No halt criteria","")),IF(C57="Check downstream",IF(J57="","No downstream system named",IF(K57="","No team named for its pipeline",IF(L57="Partial","Output contract only partial",IF(L57&lt;&gt;"Yes","No output contract",IF(M57&lt;&gt;"Yes","Contract not verified before deploy",IF(N57&lt;&gt;"Yes","Cannot switch on together",IF(O57="","Nobody named who can halt",""))))))),IF(C57="Track",IF(P57="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -5408,7 +5408,7 @@
         <v/>
       </c>
       <c r="R58" s="8">
-        <f>IF(C58="","",IF(C58="Block",IF(OR(E58="",E58&lt;1),"No trials set",IF(F58="","Trials that must pass not set",IF(F58&lt;E58,"Trials that must pass is lower than trials",IF(F58&gt;E58,"Trials that must pass is more than trials",IF(AND(D58&lt;&gt;"Yes",E58&lt;$C$47),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C58="Human decides",IF(G58="","No owner",IF(I58&lt;&gt;"Yes","No halt criteria","")),IF(C58="Check downstream",IF(J58="","No downstream system named",IF(K58="","No team named for its pipeline",IF(L58="Partial","Output contract only partial",IF(L58&lt;&gt;"Yes","No output contract",IF(M58&lt;&gt;"Yes","Contract not verified before deploy",IF(N58&lt;&gt;"Yes","Cannot switch on together",IF(O58="","Nobody named who can halt",""))))))),IF(C58="Track",IF(P58="","No owner",""),"")))))</f>
+        <f>IF(C58="","",IF(C58="Block",IF(OR(E58="",E58&lt;1),"No trials set",IF(F58="","Trials that must pass not set",IF(F58&lt;E58,"Trials that must pass is lower than trials",IF(F58&gt;E58,"Trials that must pass is more than trials",IF(AND(D58&lt;&gt;"Yes",E58&lt;IF($C$47="",3,$C$47)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C58="Human decides",IF(G58="","No owner",IF(I58&lt;&gt;"Yes","No halt criteria","")),IF(C58="Check downstream",IF(J58="","No downstream system named",IF(K58="","No team named for its pipeline",IF(L58="Partial","Output contract only partial",IF(L58&lt;&gt;"Yes","No output contract",IF(M58&lt;&gt;"Yes","Contract not verified before deploy",IF(N58&lt;&gt;"Yes","Cannot switch on together",IF(O58="","Nobody named who can halt",""))))))),IF(C58="Track",IF(P58="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -5445,7 +5445,7 @@
         <v/>
       </c>
       <c r="R59" s="8">
-        <f>IF(C59="","",IF(C59="Block",IF(OR(E59="",E59&lt;1),"No trials set",IF(F59="","Trials that must pass not set",IF(F59&lt;E59,"Trials that must pass is lower than trials",IF(F59&gt;E59,"Trials that must pass is more than trials",IF(AND(D59&lt;&gt;"Yes",E59&lt;$C$47),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C59="Human decides",IF(G59="","No owner",IF(I59&lt;&gt;"Yes","No halt criteria","")),IF(C59="Check downstream",IF(J59="","No downstream system named",IF(K59="","No team named for its pipeline",IF(L59="Partial","Output contract only partial",IF(L59&lt;&gt;"Yes","No output contract",IF(M59&lt;&gt;"Yes","Contract not verified before deploy",IF(N59&lt;&gt;"Yes","Cannot switch on together",IF(O59="","Nobody named who can halt",""))))))),IF(C59="Track",IF(P59="","No owner",""),"")))))</f>
+        <f>IF(C59="","",IF(C59="Block",IF(OR(E59="",E59&lt;1),"No trials set",IF(F59="","Trials that must pass not set",IF(F59&lt;E59,"Trials that must pass is lower than trials",IF(F59&gt;E59,"Trials that must pass is more than trials",IF(AND(D59&lt;&gt;"Yes",E59&lt;IF($C$47="",3,$C$47)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C59="Human decides",IF(G59="","No owner",IF(I59&lt;&gt;"Yes","No halt criteria","")),IF(C59="Check downstream",IF(J59="","No downstream system named",IF(K59="","No team named for its pipeline",IF(L59="Partial","Output contract only partial",IF(L59&lt;&gt;"Yes","No output contract",IF(M59&lt;&gt;"Yes","Contract not verified before deploy",IF(N59&lt;&gt;"Yes","Cannot switch on together",IF(O59="","Nobody named who can halt",""))))))),IF(C59="Track",IF(P59="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
         <v/>
       </c>
       <c r="R60" s="8">
-        <f>IF(C60="","",IF(C60="Block",IF(OR(E60="",E60&lt;1),"No trials set",IF(F60="","Trials that must pass not set",IF(F60&lt;E60,"Trials that must pass is lower than trials",IF(F60&gt;E60,"Trials that must pass is more than trials",IF(AND(D60&lt;&gt;"Yes",E60&lt;$C$47),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C60="Human decides",IF(G60="","No owner",IF(I60&lt;&gt;"Yes","No halt criteria","")),IF(C60="Check downstream",IF(J60="","No downstream system named",IF(K60="","No team named for its pipeline",IF(L60="Partial","Output contract only partial",IF(L60&lt;&gt;"Yes","No output contract",IF(M60&lt;&gt;"Yes","Contract not verified before deploy",IF(N60&lt;&gt;"Yes","Cannot switch on together",IF(O60="","Nobody named who can halt",""))))))),IF(C60="Track",IF(P60="","No owner",""),"")))))</f>
+        <f>IF(C60="","",IF(C60="Block",IF(OR(E60="",E60&lt;1),"No trials set",IF(F60="","Trials that must pass not set",IF(F60&lt;E60,"Trials that must pass is lower than trials",IF(F60&gt;E60,"Trials that must pass is more than trials",IF(AND(D60&lt;&gt;"Yes",E60&lt;IF($C$47="",3,$C$47)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C60="Human decides",IF(G60="","No owner",IF(I60&lt;&gt;"Yes","No halt criteria","")),IF(C60="Check downstream",IF(J60="","No downstream system named",IF(K60="","No team named for its pipeline",IF(L60="Partial","Output contract only partial",IF(L60&lt;&gt;"Yes","No output contract",IF(M60&lt;&gt;"Yes","Contract not verified before deploy",IF(N60&lt;&gt;"Yes","Cannot switch on together",IF(O60="","Nobody named who can halt",""))))))),IF(C60="Track",IF(P60="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -5519,7 +5519,7 @@
         <v/>
       </c>
       <c r="R61" s="8">
-        <f>IF(C61="","",IF(C61="Block",IF(OR(E61="",E61&lt;1),"No trials set",IF(F61="","Trials that must pass not set",IF(F61&lt;E61,"Trials that must pass is lower than trials",IF(F61&gt;E61,"Trials that must pass is more than trials",IF(AND(D61&lt;&gt;"Yes",E61&lt;$C$47),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C61="Human decides",IF(G61="","No owner",IF(I61&lt;&gt;"Yes","No halt criteria","")),IF(C61="Check downstream",IF(J61="","No downstream system named",IF(K61="","No team named for its pipeline",IF(L61="Partial","Output contract only partial",IF(L61&lt;&gt;"Yes","No output contract",IF(M61&lt;&gt;"Yes","Contract not verified before deploy",IF(N61&lt;&gt;"Yes","Cannot switch on together",IF(O61="","Nobody named who can halt",""))))))),IF(C61="Track",IF(P61="","No owner",""),"")))))</f>
+        <f>IF(C61="","",IF(C61="Block",IF(OR(E61="",E61&lt;1),"No trials set",IF(F61="","Trials that must pass not set",IF(F61&lt;E61,"Trials that must pass is lower than trials",IF(F61&gt;E61,"Trials that must pass is more than trials",IF(AND(D61&lt;&gt;"Yes",E61&lt;IF($C$47="",3,$C$47)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C61="Human decides",IF(G61="","No owner",IF(I61&lt;&gt;"Yes","No halt criteria","")),IF(C61="Check downstream",IF(J61="","No downstream system named",IF(K61="","No team named for its pipeline",IF(L61="Partial","Output contract only partial",IF(L61&lt;&gt;"Yes","No output contract",IF(M61&lt;&gt;"Yes","Contract not verified before deploy",IF(N61&lt;&gt;"Yes","Cannot switch on together",IF(O61="","Nobody named who can halt",""))))))),IF(C61="Track",IF(P61="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
         <v/>
       </c>
       <c r="R62" s="8">
-        <f>IF(C62="","",IF(C62="Block",IF(OR(E62="",E62&lt;1),"No trials set",IF(F62="","Trials that must pass not set",IF(F62&lt;E62,"Trials that must pass is lower than trials",IF(F62&gt;E62,"Trials that must pass is more than trials",IF(AND(D62&lt;&gt;"Yes",E62&lt;$C$47),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C62="Human decides",IF(G62="","No owner",IF(I62&lt;&gt;"Yes","No halt criteria","")),IF(C62="Check downstream",IF(J62="","No downstream system named",IF(K62="","No team named for its pipeline",IF(L62="Partial","Output contract only partial",IF(L62&lt;&gt;"Yes","No output contract",IF(M62&lt;&gt;"Yes","Contract not verified before deploy",IF(N62&lt;&gt;"Yes","Cannot switch on together",IF(O62="","Nobody named who can halt",""))))))),IF(C62="Track",IF(P62="","No owner",""),"")))))</f>
+        <f>IF(C62="","",IF(C62="Block",IF(OR(E62="",E62&lt;1),"No trials set",IF(F62="","Trials that must pass not set",IF(F62&lt;E62,"Trials that must pass is lower than trials",IF(F62&gt;E62,"Trials that must pass is more than trials",IF(AND(D62&lt;&gt;"Yes",E62&lt;IF($C$47="",3,$C$47)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C62="Human decides",IF(G62="","No owner",IF(I62&lt;&gt;"Yes","No halt criteria","")),IF(C62="Check downstream",IF(J62="","No downstream system named",IF(K62="","No team named for its pipeline",IF(L62="Partial","Output contract only partial",IF(L62&lt;&gt;"Yes","No output contract",IF(M62&lt;&gt;"Yes","Contract not verified before deploy",IF(N62&lt;&gt;"Yes","Cannot switch on together",IF(O62="","Nobody named who can halt",""))))))),IF(C62="Track",IF(P62="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -5593,7 +5593,7 @@
         <v/>
       </c>
       <c r="R63" s="8">
-        <f>IF(C63="","",IF(C63="Block",IF(OR(E63="",E63&lt;1),"No trials set",IF(F63="","Trials that must pass not set",IF(F63&lt;E63,"Trials that must pass is lower than trials",IF(F63&gt;E63,"Trials that must pass is more than trials",IF(AND(D63&lt;&gt;"Yes",E63&lt;$C$47),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C63="Human decides",IF(G63="","No owner",IF(I63&lt;&gt;"Yes","No halt criteria","")),IF(C63="Check downstream",IF(J63="","No downstream system named",IF(K63="","No team named for its pipeline",IF(L63="Partial","Output contract only partial",IF(L63&lt;&gt;"Yes","No output contract",IF(M63&lt;&gt;"Yes","Contract not verified before deploy",IF(N63&lt;&gt;"Yes","Cannot switch on together",IF(O63="","Nobody named who can halt",""))))))),IF(C63="Track",IF(P63="","No owner",""),"")))))</f>
+        <f>IF(C63="","",IF(C63="Block",IF(OR(E63="",E63&lt;1),"No trials set",IF(F63="","Trials that must pass not set",IF(F63&lt;E63,"Trials that must pass is lower than trials",IF(F63&gt;E63,"Trials that must pass is more than trials",IF(AND(D63&lt;&gt;"Yes",E63&lt;IF($C$47="",3,$C$47)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C63="Human decides",IF(G63="","No owner",IF(I63&lt;&gt;"Yes","No halt criteria","")),IF(C63="Check downstream",IF(J63="","No downstream system named",IF(K63="","No team named for its pipeline",IF(L63="Partial","Output contract only partial",IF(L63&lt;&gt;"Yes","No output contract",IF(M63&lt;&gt;"Yes","Contract not verified before deploy",IF(N63&lt;&gt;"Yes","Cannot switch on together",IF(O63="","Nobody named who can halt",""))))))),IF(C63="Track",IF(P63="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
         <v/>
       </c>
       <c r="R64" s="8">
-        <f>IF(C64="","",IF(C64="Block",IF(OR(E64="",E64&lt;1),"No trials set",IF(F64="","Trials that must pass not set",IF(F64&lt;E64,"Trials that must pass is lower than trials",IF(F64&gt;E64,"Trials that must pass is more than trials",IF(AND(D64&lt;&gt;"Yes",E64&lt;$C$47),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C64="Human decides",IF(G64="","No owner",IF(I64&lt;&gt;"Yes","No halt criteria","")),IF(C64="Check downstream",IF(J64="","No downstream system named",IF(K64="","No team named for its pipeline",IF(L64="Partial","Output contract only partial",IF(L64&lt;&gt;"Yes","No output contract",IF(M64&lt;&gt;"Yes","Contract not verified before deploy",IF(N64&lt;&gt;"Yes","Cannot switch on together",IF(O64="","Nobody named who can halt",""))))))),IF(C64="Track",IF(P64="","No owner",""),"")))))</f>
+        <f>IF(C64="","",IF(C64="Block",IF(OR(E64="",E64&lt;1),"No trials set",IF(F64="","Trials that must pass not set",IF(F64&lt;E64,"Trials that must pass is lower than trials",IF(F64&gt;E64,"Trials that must pass is more than trials",IF(AND(D64&lt;&gt;"Yes",E64&lt;IF($C$47="",3,$C$47)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C64="Human decides",IF(G64="","No owner",IF(I64&lt;&gt;"Yes","No halt criteria","")),IF(C64="Check downstream",IF(J64="","No downstream system named",IF(K64="","No team named for its pipeline",IF(L64="Partial","Output contract only partial",IF(L64&lt;&gt;"Yes","No output contract",IF(M64&lt;&gt;"Yes","Contract not verified before deploy",IF(N64&lt;&gt;"Yes","Cannot switch on together",IF(O64="","Nobody named who can halt",""))))))),IF(C64="Track",IF(P64="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
         <v/>
       </c>
       <c r="R65" s="8">
-        <f>IF(C65="","",IF(C65="Block",IF(OR(E65="",E65&lt;1),"No trials set",IF(F65="","Trials that must pass not set",IF(F65&lt;E65,"Trials that must pass is lower than trials",IF(F65&gt;E65,"Trials that must pass is more than trials",IF(AND(D65&lt;&gt;"Yes",E65&lt;$C$47),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C65="Human decides",IF(G65="","No owner",IF(I65&lt;&gt;"Yes","No halt criteria","")),IF(C65="Check downstream",IF(J65="","No downstream system named",IF(K65="","No team named for its pipeline",IF(L65="Partial","Output contract only partial",IF(L65&lt;&gt;"Yes","No output contract",IF(M65&lt;&gt;"Yes","Contract not verified before deploy",IF(N65&lt;&gt;"Yes","Cannot switch on together",IF(O65="","Nobody named who can halt",""))))))),IF(C65="Track",IF(P65="","No owner",""),"")))))</f>
+        <f>IF(C65="","",IF(C65="Block",IF(OR(E65="",E65&lt;1),"No trials set",IF(F65="","Trials that must pass not set",IF(F65&lt;E65,"Trials that must pass is lower than trials",IF(F65&gt;E65,"Trials that must pass is more than trials",IF(AND(D65&lt;&gt;"Yes",E65&lt;IF($C$47="",3,$C$47)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C65="Human decides",IF(G65="","No owner",IF(I65&lt;&gt;"Yes","No halt criteria","")),IF(C65="Check downstream",IF(J65="","No downstream system named",IF(K65="","No team named for its pipeline",IF(L65="Partial","Output contract only partial",IF(L65&lt;&gt;"Yes","No output contract",IF(M65&lt;&gt;"Yes","Contract not verified before deploy",IF(N65&lt;&gt;"Yes","Cannot switch on together",IF(O65="","Nobody named who can halt",""))))))),IF(C65="Track",IF(P65="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -5704,7 +5704,7 @@
         <v/>
       </c>
       <c r="R66" s="8">
-        <f>IF(C66="","",IF(C66="Block",IF(OR(E66="",E66&lt;1),"No trials set",IF(F66="","Trials that must pass not set",IF(F66&lt;E66,"Trials that must pass is lower than trials",IF(F66&gt;E66,"Trials that must pass is more than trials",IF(AND(D66&lt;&gt;"Yes",E66&lt;$C$47),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C66="Human decides",IF(G66="","No owner",IF(I66&lt;&gt;"Yes","No halt criteria","")),IF(C66="Check downstream",IF(J66="","No downstream system named",IF(K66="","No team named for its pipeline",IF(L66="Partial","Output contract only partial",IF(L66&lt;&gt;"Yes","No output contract",IF(M66&lt;&gt;"Yes","Contract not verified before deploy",IF(N66&lt;&gt;"Yes","Cannot switch on together",IF(O66="","Nobody named who can halt",""))))))),IF(C66="Track",IF(P66="","No owner",""),"")))))</f>
+        <f>IF(C66="","",IF(C66="Block",IF(OR(E66="",E66&lt;1),"No trials set",IF(F66="","Trials that must pass not set",IF(F66&lt;E66,"Trials that must pass is lower than trials",IF(F66&gt;E66,"Trials that must pass is more than trials",IF(AND(D66&lt;&gt;"Yes",E66&lt;IF($C$47="",3,$C$47)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C66="Human decides",IF(G66="","No owner",IF(I66&lt;&gt;"Yes","No halt criteria","")),IF(C66="Check downstream",IF(J66="","No downstream system named",IF(K66="","No team named for its pipeline",IF(L66="Partial","Output contract only partial",IF(L66&lt;&gt;"Yes","No output contract",IF(M66&lt;&gt;"Yes","Contract not verified before deploy",IF(N66&lt;&gt;"Yes","Cannot switch on together",IF(O66="","Nobody named who can halt",""))))))),IF(C66="Track",IF(P66="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
         <v/>
       </c>
       <c r="R67" s="8">
-        <f>IF(C67="","",IF(C67="Block",IF(OR(E67="",E67&lt;1),"No trials set",IF(F67="","Trials that must pass not set",IF(F67&lt;E67,"Trials that must pass is lower than trials",IF(F67&gt;E67,"Trials that must pass is more than trials",IF(AND(D67&lt;&gt;"Yes",E67&lt;$C$47),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C67="Human decides",IF(G67="","No owner",IF(I67&lt;&gt;"Yes","No halt criteria","")),IF(C67="Check downstream",IF(J67="","No downstream system named",IF(K67="","No team named for its pipeline",IF(L67="Partial","Output contract only partial",IF(L67&lt;&gt;"Yes","No output contract",IF(M67&lt;&gt;"Yes","Contract not verified before deploy",IF(N67&lt;&gt;"Yes","Cannot switch on together",IF(O67="","Nobody named who can halt",""))))))),IF(C67="Track",IF(P67="","No owner",""),"")))))</f>
+        <f>IF(C67="","",IF(C67="Block",IF(OR(E67="",E67&lt;1),"No trials set",IF(F67="","Trials that must pass not set",IF(F67&lt;E67,"Trials that must pass is lower than trials",IF(F67&gt;E67,"Trials that must pass is more than trials",IF(AND(D67&lt;&gt;"Yes",E67&lt;IF($C$47="",3,$C$47)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C67="Human decides",IF(G67="","No owner",IF(I67&lt;&gt;"Yes","No halt criteria","")),IF(C67="Check downstream",IF(J67="","No downstream system named",IF(K67="","No team named for its pipeline",IF(L67="Partial","Output contract only partial",IF(L67&lt;&gt;"Yes","No output contract",IF(M67&lt;&gt;"Yes","Contract not verified before deploy",IF(N67&lt;&gt;"Yes","Cannot switch on together",IF(O67="","Nobody named who can halt",""))))))),IF(C67="Track",IF(P67="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
         <v/>
       </c>
       <c r="R68" s="8">
-        <f>IF(C68="","",IF(C68="Block",IF(OR(E68="",E68&lt;1),"No trials set",IF(F68="","Trials that must pass not set",IF(F68&lt;E68,"Trials that must pass is lower than trials",IF(F68&gt;E68,"Trials that must pass is more than trials",IF(AND(D68&lt;&gt;"Yes",E68&lt;$C$47),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C68="Human decides",IF(G68="","No owner",IF(I68&lt;&gt;"Yes","No halt criteria","")),IF(C68="Check downstream",IF(J68="","No downstream system named",IF(K68="","No team named for its pipeline",IF(L68="Partial","Output contract only partial",IF(L68&lt;&gt;"Yes","No output contract",IF(M68&lt;&gt;"Yes","Contract not verified before deploy",IF(N68&lt;&gt;"Yes","Cannot switch on together",IF(O68="","Nobody named who can halt",""))))))),IF(C68="Track",IF(P68="","No owner",""),"")))))</f>
+        <f>IF(C68="","",IF(C68="Block",IF(OR(E68="",E68&lt;1),"No trials set",IF(F68="","Trials that must pass not set",IF(F68&lt;E68,"Trials that must pass is lower than trials",IF(F68&gt;E68,"Trials that must pass is more than trials",IF(AND(D68&lt;&gt;"Yes",E68&lt;IF($C$47="",3,$C$47)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C68="Human decides",IF(G68="","No owner",IF(I68&lt;&gt;"Yes","No halt criteria","")),IF(C68="Check downstream",IF(J68="","No downstream system named",IF(K68="","No team named for its pipeline",IF(L68="Partial","Output contract only partial",IF(L68&lt;&gt;"Yes","No output contract",IF(M68&lt;&gt;"Yes","Contract not verified before deploy",IF(N68&lt;&gt;"Yes","Cannot switch on together",IF(O68="","Nobody named who can halt",""))))))),IF(C68="Track",IF(P68="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -5815,7 +5815,7 @@
         <v/>
       </c>
       <c r="R69" s="8">
-        <f>IF(C69="","",IF(C69="Block",IF(OR(E69="",E69&lt;1),"No trials set",IF(F69="","Trials that must pass not set",IF(F69&lt;E69,"Trials that must pass is lower than trials",IF(F69&gt;E69,"Trials that must pass is more than trials",IF(AND(D69&lt;&gt;"Yes",E69&lt;$C$47),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C69="Human decides",IF(G69="","No owner",IF(I69&lt;&gt;"Yes","No halt criteria","")),IF(C69="Check downstream",IF(J69="","No downstream system named",IF(K69="","No team named for its pipeline",IF(L69="Partial","Output contract only partial",IF(L69&lt;&gt;"Yes","No output contract",IF(M69&lt;&gt;"Yes","Contract not verified before deploy",IF(N69&lt;&gt;"Yes","Cannot switch on together",IF(O69="","Nobody named who can halt",""))))))),IF(C69="Track",IF(P69="","No owner",""),"")))))</f>
+        <f>IF(C69="","",IF(C69="Block",IF(OR(E69="",E69&lt;1),"No trials set",IF(F69="","Trials that must pass not set",IF(F69&lt;E69,"Trials that must pass is lower than trials",IF(F69&gt;E69,"Trials that must pass is more than trials",IF(AND(D69&lt;&gt;"Yes",E69&lt;IF($C$47="",3,$C$47)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C69="Human decides",IF(G69="","No owner",IF(I69&lt;&gt;"Yes","No halt criteria","")),IF(C69="Check downstream",IF(J69="","No downstream system named",IF(K69="","No team named for its pipeline",IF(L69="Partial","Output contract only partial",IF(L69&lt;&gt;"Yes","No output contract",IF(M69&lt;&gt;"Yes","Contract not verified before deploy",IF(N69&lt;&gt;"Yes","Cannot switch on together",IF(O69="","Nobody named who can halt",""))))))),IF(C69="Track",IF(P69="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>
@@ -5852,7 +5852,7 @@
         <v/>
       </c>
       <c r="R70" s="8">
-        <f>IF(C70="","",IF(C70="Block",IF(OR(E70="",E70&lt;1),"No trials set",IF(F70="","Trials that must pass not set",IF(F70&lt;E70,"Trials that must pass is lower than trials",IF(F70&gt;E70,"Trials that must pass is more than trials",IF(AND(D70&lt;&gt;"Yes",E70&lt;$C$47),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C70="Human decides",IF(G70="","No owner",IF(I70&lt;&gt;"Yes","No halt criteria","")),IF(C70="Check downstream",IF(J70="","No downstream system named",IF(K70="","No team named for its pipeline",IF(L70="Partial","Output contract only partial",IF(L70&lt;&gt;"Yes","No output contract",IF(M70&lt;&gt;"Yes","Contract not verified before deploy",IF(N70&lt;&gt;"Yes","Cannot switch on together",IF(O70="","Nobody named who can halt",""))))))),IF(C70="Track",IF(P70="","No owner",""),"")))))</f>
+        <f>IF(C70="","",IF(C70="Block",IF(OR(E70="",E70&lt;1),"No trials set",IF(F70="","Trials that must pass not set",IF(F70&lt;E70,"Trials that must pass is lower than trials",IF(F70&gt;E70,"Trials that must pass is more than trials",IF(AND(D70&lt;&gt;"Yes",E70&lt;IF($C$47="",3,$C$47)),"Fewer trials than the minimum for non-deterministic cases",""))))),IF(C70="Human decides",IF(G70="","No owner",IF(I70&lt;&gt;"Yes","No halt criteria","")),IF(C70="Check downstream",IF(J70="","No downstream system named",IF(K70="","No team named for its pipeline",IF(L70="Partial","Output contract only partial",IF(L70&lt;&gt;"Yes","No output contract",IF(M70&lt;&gt;"Yes","Contract not verified before deploy",IF(N70&lt;&gt;"Yes","Cannot switch on together",IF(O70="","Nobody named who can halt",""))))))),IF(C70="Track",IF(P70="","No owner",""),"")))))</f>
         <v/>
       </c>
     </row>

--- a/downloads/gate-routing-map.xlsx
+++ b/downloads/gate-routing-map.xlsx
@@ -2050,19 +2050,19 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation sqref="D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
+    <dataValidation sqref="D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
       <formula1>$Z$1:$Z$2</formula1>
     </dataValidation>
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
       <formula1>$Z$4:$Z$7</formula1>
     </dataValidation>
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
       <formula1>$Z$9:$Z$11</formula1>
     </dataValidation>
-    <dataValidation sqref="G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
+    <dataValidation sqref="G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
       <formula1>$Z$13:$Z$14</formula1>
     </dataValidation>
-    <dataValidation sqref="J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
+    <dataValidation sqref="J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
       <formula1>$Z$16:$Z$19</formula1>
     </dataValidation>
   </dataValidations>
@@ -3245,25 +3245,25 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="7">
-    <dataValidation sqref="C5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Minimum trials" error="Enter a whole number of 1 or more." type="whole" operator="greaterThanOrEqual">
+    <dataValidation sqref="C5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Minimum trials" error="Enter a whole number of 1 or more." type="whole" operator="greaterThanOrEqual">
       <formula1>1</formula1>
     </dataValidation>
-    <dataValidation sqref="I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
+    <dataValidation sqref="I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
       <formula1>$Z$1:$Z$2</formula1>
     </dataValidation>
-    <dataValidation sqref="L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
+    <dataValidation sqref="L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
       <formula1>$Z$4:$Z$6</formula1>
     </dataValidation>
-    <dataValidation sqref="E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Trials" error="Enter a whole number of trials." type="whole" operator="greaterThanOrEqual">
+    <dataValidation sqref="E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Trials" error="Enter a whole number of trials." type="whole" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not this route" error="This column is for Human decides cases. Change the route on the Gate Inventory first." type="custom">
+    <dataValidation sqref="G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not this route" error="This column is for Human decides cases. Change the route on the Gate Inventory first." type="custom">
       <formula1>$C9="Human decides"</formula1>
     </dataValidation>
-    <dataValidation sqref="J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not this route" error="This column is for Check downstream cases. Change the route on the Gate Inventory first." type="custom">
+    <dataValidation sqref="J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not this route" error="This column is for Check downstream cases. Change the route on the Gate Inventory first." type="custom">
       <formula1>$C9="Check downstream"</formula1>
     </dataValidation>
-    <dataValidation sqref="P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not this route" error="This column is for Track cases. Change the route on the Gate Inventory first." type="custom">
+    <dataValidation sqref="P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not this route" error="This column is for Track cases. Change the route on the Gate Inventory first." type="custom">
       <formula1>$C9="Track"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3755,7 +3755,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E11 E12 E13 E14 E15 E16 E17 E18 E19 E20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
+    <dataValidation sqref="E11 E12 E13 E14 E15 E16 E17 E18 E19 E20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
       <formula1>$Z$1:$Z$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -6606,37 +6606,37 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="11">
-    <dataValidation sqref="D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
+    <dataValidation sqref="D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
       <formula1>$Z$1:$Z$2</formula1>
     </dataValidation>
-    <dataValidation sqref="E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
+    <dataValidation sqref="E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
       <formula1>$Z$4:$Z$7</formula1>
     </dataValidation>
-    <dataValidation sqref="F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
+    <dataValidation sqref="F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
       <formula1>$Z$9:$Z$11</formula1>
     </dataValidation>
-    <dataValidation sqref="G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 I51 I52 I53 I54 I55 I56 I57 I58 I59 I60 I61 I62 I63 I64 I65 I66 I67 I68 I69 I70 M51 M52 M53 M54 M55 M56 M57 M58 M59 M60 M61 M62 M63 M64 M65 M66 M67 M68 M69 M70 N51 N52 N53 N54 N55 N56 N57 N58 N59 N60 N61 N62 N63 N64 N65 N66 N67 N68 N69 N70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
+    <dataValidation sqref="G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 I51 I52 I53 I54 I55 I56 I57 I58 I59 I60 I61 I62 I63 I64 I65 I66 I67 I68 I69 I70 M51 M52 M53 M54 M55 M56 M57 M58 M59 M60 M61 M62 M63 M64 M65 M66 M67 M68 M69 M70 N51 N52 N53 N54 N55 N56 N57 N58 N59 N60 N61 N62 N63 N64 N65 N66 N67 N68 N69 N70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
       <formula1>$Z$13:$Z$14</formula1>
     </dataValidation>
-    <dataValidation sqref="J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
+    <dataValidation sqref="J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
       <formula1>$Z$16:$Z$19</formula1>
     </dataValidation>
-    <dataValidation sqref="C47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Minimum trials" error="Enter a whole number of 1 or more." type="whole" operator="greaterThanOrEqual">
+    <dataValidation sqref="C47" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Minimum trials" error="Enter a whole number of 1 or more." type="whole" operator="greaterThanOrEqual">
       <formula1>1</formula1>
     </dataValidation>
-    <dataValidation sqref="E96 E97 E98 E99 E100 E101 E102 E103 E104 E105 L51 L52 L53 L54 L55 L56 L57 L58 L59 L60 L61 L62 L63 L64 L65 L66 L67 L68 L69 L70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
+    <dataValidation sqref="E96 E97 E98 E99 E100 E101 E102 E103 E104 E105 L51 L52 L53 L54 L55 L56 L57 L58 L59 L60 L61 L62 L63 L64 L65 L66 L67 L68 L69 L70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
       <formula1>$Z$21:$Z$23</formula1>
     </dataValidation>
-    <dataValidation sqref="E51 E52 E53 E54 E55 E56 E57 E58 E59 E60 E61 E62 E63 E64 E65 E66 E67 E68 E69 E70 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Trials" error="Enter a whole number of trials." type="whole" operator="greaterThanOrEqual">
+    <dataValidation sqref="E51 E52 E53 E54 E55 E56 E57 E58 E59 E60 E61 E62 E63 E64 E65 E66 E67 E68 E69 E70 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Trials" error="Enter a whole number of trials." type="whole" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="G51 G52 G53 G54 G55 G56 G57 G58 G59 G60 G61 G62 G63 G64 G65 G66 G67 G68 G69 G70 H51 H52 H53 H54 H55 H56 H57 H58 H59 H60 H61 H62 H63 H64 H65 H66 H67 H68 H69 H70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not this route" error="This column is for Human decides cases. Change the route on the Gate Inventory first." type="custom">
+    <dataValidation sqref="G51 G52 G53 G54 G55 G56 G57 G58 G59 G60 G61 G62 G63 G64 G65 G66 G67 G68 G69 G70 H51 H52 H53 H54 H55 H56 H57 H58 H59 H60 H61 H62 H63 H64 H65 H66 H67 H68 H69 H70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not this route" error="This column is for Human decides cases. Change the route on the Gate Inventory first." type="custom">
       <formula1>$C51="Human decides"</formula1>
     </dataValidation>
-    <dataValidation sqref="J51 J52 J53 J54 J55 J56 J57 J58 J59 J60 J61 J62 J63 J64 J65 J66 J67 J68 J69 J70 K51 K52 K53 K54 K55 K56 K57 K58 K59 K60 K61 K62 K63 K64 K65 K66 K67 K68 K69 K70 O51 O52 O53 O54 O55 O56 O57 O58 O59 O60 O61 O62 O63 O64 O65 O66 O67 O68 O69 O70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not this route" error="This column is for Check downstream cases. Change the route on the Gate Inventory first." type="custom">
+    <dataValidation sqref="J51 J52 J53 J54 J55 J56 J57 J58 J59 J60 J61 J62 J63 J64 J65 J66 J67 J68 J69 J70 K51 K52 K53 K54 K55 K56 K57 K58 K59 K60 K61 K62 K63 K64 K65 K66 K67 K68 K69 K70 O51 O52 O53 O54 O55 O56 O57 O58 O59 O60 O61 O62 O63 O64 O65 O66 O67 O68 O69 O70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not this route" error="This column is for Check downstream cases. Change the route on the Gate Inventory first." type="custom">
       <formula1>$C51="Check downstream"</formula1>
     </dataValidation>
-    <dataValidation sqref="P51 P52 P53 P54 P55 P56 P57 P58 P59 P60 P61 P62 P63 P64 P65 P66 P67 P68 P69 P70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not this route" error="This column is for Track cases. Change the route on the Gate Inventory first." type="custom">
+    <dataValidation sqref="P51 P52 P53 P54 P55 P56 P57 P58 P59 P60 P61 P62 P63 P64 P65 P66 P67 P68 P69 P70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not this route" error="This column is for Track cases. Change the route on the Gate Inventory first." type="custom">
       <formula1>$C51="Track"</formula1>
     </dataValidation>
   </dataValidations>
